--- a/docs/video_manual/v1.6/exports/Report_Customer-type-wise.xlsx
+++ b/docs/video_manual/v1.6/exports/Report_Customer-type-wise.xlsx
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 18-10-2026 00:47 by Master Administrator</t>
+          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 21-10-2026 05:16 by Master Administrator</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
         <v>119900</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>682.01</v>
+        <v>682</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>18.94</v>
@@ -565,13 +565,13 @@
         <v>90250</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>750.01</v>
+        <v>805</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>28.85</v>
+        <v>30.96</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="7">
@@ -649,13 +649,13 @@
         <v>29900</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="10">
@@ -733,13 +733,13 @@
         <v>428700</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2456.02</v>
+        <v>2637</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>19.34</v>
+        <v>20.76</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>

--- a/docs/video_manual/v1.6/exports/Report_Customer-type-wise.xlsx
+++ b/docs/video_manual/v1.6/exports/Report_Customer-type-wise.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,11 @@
       <i val="1"/>
       <color rgb="005B6675"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -70,20 +75,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,47 +478,50 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 21-10-2026 05:16 by Master Administrator</t>
-        </is>
-      </c>
+          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 21-10-2026 14:47 by Master Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Customer type</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Customers</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Invoices</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Cases</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Sales value</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Freight + pickup/auto</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Cost / case</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Cost % of sales</t>
         </is>
@@ -524,25 +533,25 @@
           <t>Stockist</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>119900</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>682</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>18.94</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -552,25 +561,25 @@
           <t>Retailer</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>90250</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>805</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>30.96</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>0.89</v>
       </c>
     </row>
@@ -580,25 +589,25 @@
           <t>Chain Pharmacy</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="B7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>71100</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>484</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>0.68</v>
       </c>
     </row>
@@ -608,25 +617,25 @@
           <t>Super Stockist</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="B8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>68200</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>440</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -636,25 +645,25 @@
           <t>Distributor</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="n">
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>29900</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="7" t="n">
         <v>0.42</v>
       </c>
     </row>
@@ -664,25 +673,25 @@
           <t>Government Supply</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="n">
+      <c r="B10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
         <v>27750</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -692,53 +701,53 @@
           <t>Hospital</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="n">
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>21600</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="6" t="n">
         <v>16.67</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="9" t="n">
         <v>127</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="10" t="n">
         <v>428700</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="10" t="n">
         <v>2637</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="10" t="n">
         <v>20.76</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="11" t="n">
         <v>0.62</v>
       </c>
     </row>
